--- a/www/download/IND.compensation.emp.s.us.rpO1.xlsx
+++ b/www/download/IND.compensation.emp.s.us.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247042.561166084</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245212.233573625</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218661.70000032</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236203.455246225</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226529.411581485</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211426.463917418</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234743.684481662</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>298459.503014282</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>362225.598050155</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>401895.913603307</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>434454.075255592</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>525383.13595245</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>581746.34502725</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>567463.067505893</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149675.606169677</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145738.318632223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128695.957262441</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131521.983285444</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130408.256575546</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117186.843937276</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115641.130433391</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124600.275081746</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152362.597063906</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171096.132710131</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177805.570901088</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187820.15928529</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214640.180802592</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244328.853363102</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>230988.738402635</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166925.935825279</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150238.850509246</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152780.082432811</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153789.385768597</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139092.734411134</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142257.524134406</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155622.068038809</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189850.98373018</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214418.395190387</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221372.722061265</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233856.294647683</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268463.02295684</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304290.862609071</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291661.720887746</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6217.29677098901</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4798.85981629446</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6259.01049800769</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6036.95211304725</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5484.63915254219</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5928.87398593274</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6628.1048903259</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8671.86455135768</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10430.9043908861</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11518.9534811051</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12840.3745381041</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16776.530543474</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21718.3063310489</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22406.6496559926</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>386261.837240327</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382909.754649366</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374196.607393886</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>255838.859720888</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278432.354738735</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239810.05324894</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>220899.745023004</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231929.903542001</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>274582.276132272</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374878.242364804</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>473406.172577666</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>694954.107433865</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>836641.718047541</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>846505.046696694</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>321482.530872517</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>332555.747059074</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>344917.178394306</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338568.917487131</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356999.020180108</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386874.946130793</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386772.922543959</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>396942.807451827</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466382.371783055</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>530121.617754663</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>600740.325966168</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>683381.60813677</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760024.789437084</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810776.88984777</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>719123.923659109</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467727.886435222</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515800.335953662</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542539.536153294</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>563860.76736749</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>607903.674040208</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>659006.88251917</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>707407.939686337</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>777143.095397519</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>900055.312694353</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018459.84835292</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1182195.15416825</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1468707.44826045</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>1905657.48987876</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>2087894.22134836</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5428.85074392709</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5270.72917188927</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5483.52170324111</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5598.45614178127</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5290.57706587232</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5477.72397844922</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6144.2804408705</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8016.30446858495</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9440.96012703077</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10170.0773856905</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10905.9669471042</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12486.3005746237</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14467.4037383969</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13817.1416338568</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32631.1792220981</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30678.5639491407</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32059.7484407347</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30953.1831688823</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29538.7840449964</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32567.5223859693</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41127.6238857033</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51135.9488229703</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59309.022845279</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67189.3686554274</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76949.7458276835</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93596.0911283756</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119867.694073496</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103968.870192087</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1502412.29547561</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1317411.14858811</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1326358.61866775</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.302</t>
+          <t>1302406.93863858</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1172559.80554357</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1158039.93511591</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1229729.51173504</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1479553.94155057</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1638875.00976356</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1637759.62104069</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>1677285.14398029</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.876</t>
+          <t>1875703.64141804</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>2097001.03153539</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>2017691.93984275</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105475.073243332</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96758.6284176353</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100831.035595434</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101218.949515811</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91433.6251083937</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93025.9601306236</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102246.71517741</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>125590.118048088</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141688.54413748</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148070.084821056</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157652.834543269</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182898.0467475</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>206255.911435343</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>196642.801807363</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>358083.445359631</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>372331.088725999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>342997.313917794</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>358380.819232282</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366035.373843655</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338929.567248008</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>351984.377498107</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>392605.991558936</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>498162.302385956</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>578956.463825489</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>620027.285849691</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>673117.318416295</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>792753.100788172</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>902445.44325516</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>835809.727677538</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2163.1993614518</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2598.52951763284</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2685.60327370236</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2952.21889994261</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2924.45257344085</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2873.44566883691</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3049.05306926796</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3570.04041898114</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4873.65566729071</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6061.3972959849</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6760.24191490913</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8225.85810822455</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11192.336567059</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13653.5984685896</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11402.7682049438</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76548.6526088396</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75928.4406545897</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70740.1372455899</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73138.9017173403</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73475.8848258086</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67381.129906586</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69040.5710335755</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74896.1260440397</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91922.7636145912</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105216.960221896</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110653.750386334</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116859.797080634</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134984.0403848</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154720.822196622</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145394.444269938</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>894246.998996653</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>892705.01409536</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>801013.038454619</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>819008.805657723</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>818120.744067147</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>745992.56218311</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>754751.47190718</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>829814.613127679</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1022196.98339448</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>1164259.26328522</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.208</t>
+          <t>1208123.46570889</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1272830.95291963</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1444932.84207016</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>1607162.91533441</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1522197.41274275</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729241.42651865</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>808232.241464891</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>880232.972086167</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912758.829648804</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>914475.288209213</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>920938.425083602</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>1002647.46318871</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>1155969.91713234</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1362823.71365045</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>1426225.38972571</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1522740.61097274</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1751292.93512564</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.658</t>
+          <t>1657762.14653244</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1415851.85917085</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62715.6626402422</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62295.0916240648</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63640.3871769388</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67815.6729060742</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60970.220312147</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61799.5299179561</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74908.7324890371</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98041.926950747</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115811.88345511</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122932.982734002</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134075.134062603</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157280.592704313</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180484.72896841</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177848.072136483</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24971.7648136563</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24752.0798094449</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24891.6820905812</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25207.9121430708</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24783.9985822109</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25389.3433363619</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27584.067228164</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34873.9763075699</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44286.4464960014</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53622.4462388657</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58247.945903252</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58545.1124246822</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71423.5215695397</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80623.5198120911</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65872.4146455416</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122218.850226017</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139139.692155326</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137534.487450055</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55881.1880880761</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84495.8385922481</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87083.2944607133</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82155.3075983676</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98587.9465131236</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121341.893929067</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123970.13623611</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129692.577799816</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168552.94623058</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201540.137830582</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234885.642430745</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249384.961977804</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198089.070790303</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196162.657726759</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221371.657877838</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219220.329306488</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228724.289692498</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236706.271197512</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247082.297465197</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257128.621463448</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299841.647733577</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347623.532582441</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>404651.235885026</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>454079.252238379</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>567246.968696692</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>617745.031017299</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>643862.68391602</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40364.5939571423</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42672.3483138855</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45441.7179008546</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48009.4451438283</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47248.0235749582</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50629.6601011787</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57285.7035400332</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73950.0882721045</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88451.5230381879</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98405.7780784118</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108777.262988193</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130100.676925427</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148319.207223746</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127815.480017101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>679733.554643271</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>758441.257490796</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>717904.276715278</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>703585.461813047</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>693857.950583344</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>625554.88267815</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>636125.742097246</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>700131.441621817</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>872621.151126705</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>988910.628243449</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>1029297.71456805</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1077681.83988703</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1221323.84656418</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1365623.42467672</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>1295764.70313376</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.161</t>
+          <t>3161322.34066248</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>2705927.70396172</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>2473218.33201866</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>2251829.38971421</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2522696.35008506</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.676</t>
+          <t>2675664.46797961</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.342</t>
+          <t>2341509.78794984</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>2211861.0252521</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.363</t>
+          <t>2362881.4347047</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.558</t>
+          <t>2558230.46020092</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.537</t>
+          <t>2536580.45629792</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.438</t>
+          <t>2437547.78207593</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.439</t>
+          <t>2439014.46378651</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2711916.13868508</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>2756086.66383692</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>429108.845699053</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>393881.896820065</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>257613.676550789</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312348.682631458</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353831.571985482</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>339803.996715696</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>382243.187022735</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>433445.671955757</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475287.804818375</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566607.454749689</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>633380.066717064</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>684836.2921322</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>619922.388725574</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>550345.838391702</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4413.2116762702</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4810.78304557858</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5513.89748690017</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5373.96564117383</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5163.52928834904</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5423.21665241783</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6355.59458427306</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8402.73777334017</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10486.1630721106</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12126.7510595509</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14490.2804927815</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19059.9184852712</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23934.7048099527</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18804.4211754875</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10503.4413717034</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10427.3689584264</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9558.49779111572</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9951.80022776958</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10378.5343859256</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10026.3418543322</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10624.698944257</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11924.556829957</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14711.22241411</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17060.6380435428</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18360.608648465</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19702.5215524469</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23307.9004151758</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28874.9325570042</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28408.536187663</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2433.76641698823</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2911.4719976861</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3175.20318680375</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3303.52479953617</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3550.50419662563</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3576.08119780887</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3665.28545269562</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3949.85019166349</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4870.61141889268</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5954.6074726428</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7378.38734092036</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9583.26873796141</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14776.8212147021</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18752.5633268763</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13108.3148496071</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108267.244522825</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116025.720763604</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143141.854759198</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155905.382675339</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180410.815992636</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218524.041709291</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>243641.18572786</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255166.051348419</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>243846.129181783</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249651.269514551</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>276990.218493809</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299601.081887128</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>320110.562064993</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338513.079912929</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>275214.601481728</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1951.70874750034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1896.64032042978</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1995.10864087904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2031.06693944933</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1942.8079854763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2027.75751254768</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2217.01603428793</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2649.87773934298</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3024.69870145227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3105.22631611993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3318.28575340782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3798.83718075924</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4801.04665285912</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4526.25911690874</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254812.107116176</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252872.209196045</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>230613.67452377</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241436.717045849</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246776.722249077</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229293.949001612</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237472.510775032</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262702.819050097</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>323233.238782572</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>364523.867293859</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>370710.693728264</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389610.62877315</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>449130.385402166</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>507293.478975141</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>488282.846078824</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136365.178028398</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138702.568470208</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158088.637722025</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154789.819536808</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119603.910053449</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121330.985757966</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117856.895027572</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123175.866337015</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135218.424879093</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158798.181727026</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171313.241181191</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208900.965393392</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271054.618660394</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216652.208613619</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64390.1429588036</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67805.5106716471</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64867.0389090267</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68669.0676641218</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70200.0766136047</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65915.005808849</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67564.8492680654</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74278.3257723271</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91231.3826085677</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103177.855088524</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107837.011122488</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113883.213810508</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129523.7389639</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143772.790474636</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136117.219650223</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20827.7154125453</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17878.2323324753</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25574.5068786929</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19246.946945127</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22387.8492687505</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26932.9122035333</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29223.1540073207</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38004.1607531317</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37815.7515167356</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56716.3153914071</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70036.737127413</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94380.2326877114</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120176.419878924</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91760.5600450726</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182589.786305454</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225627.675546105</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226401.480908441</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174046.030223463</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101732.70129896</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132427.198407428</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158669.464412438</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186418.259328686</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>230030.513991632</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>304889.564299288</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>376391.502262199</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>488150.895498128</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>656182.589247839</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>843107.89603508</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>637927.263060935</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6561.3869648896</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7312.97872018727</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7842.89355693317</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8135.20634611494</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7210.15848883682</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7311.75335210429</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7333.6971430638</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8486.40175983047</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11434.3765778881</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14226.8452442885</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16425.3731892327</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19014.5350364168</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25613.2077510367</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32694.8229586497</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32072.4831027948</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14513.5561779957</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13648.5087300115</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14067.2700511963</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14138.4792389739</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12828.319893295</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13125.6410110016</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14692.7626133391</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18237.6396378539</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21236.2686187478</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22383.7224061932</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24088.5110512577</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28899.233180043</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34279.4176577063</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32150.0842224023</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161542.668371692</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147085.249329839</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147365.163379276</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>146513.806072053</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145381.994219881</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136976.405454252</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149877.465676238</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>185578.561508121</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>210743.792381888</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215298.41297581</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225476.100933943</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264880.656011057</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>280324.241073704</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237231.086161039</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70161.8268922823</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83196.192142393</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91495.0230014299</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97992.2643687726</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106370.615282295</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105618.88455691</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76091.9902247633</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80176.3429900221</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102675.495454688</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131232.023706477</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165554.470880223</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>175374.24917045</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215287.382182296</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244767.100246639</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205621.912332655</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170674.531036294</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179262.534251722</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182091.650982684</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164311.131679755</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176098.037946597</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188365.268356586</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171574.566746385</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167528.333807679</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172506.401579701</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184264.398670204</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200746.334689084</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207723.236472464</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211172.142171429</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>220585.827149092</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203574.600826775</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.464</t>
+          <t>4464095.61405741</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.688</t>
+          <t>4688432.49356206</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>4974147.50682848</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5.309</t>
+          <t>5308510.72048344</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.622</t>
+          <t>5622009.90984497</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6.081</t>
+          <t>6080751.6551146</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6.309</t>
+          <t>6309483.70364426</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6460328.12366782</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>6.766</t>
+          <t>6766131.10358599</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>7.112</t>
+          <t>7111650.34206001</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>7.476</t>
+          <t>7475981.94805311</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>7.914</t>
+          <t>7914364.89918369</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>8.333</t>
+          <t>8333069.16370465</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>8.529</t>
+          <t>8528874.97863706</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8309518.9298135</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>1912553.25961093</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>2024580.61430081</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>2042561.38369465</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1955571.25946932</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>1972638.68944014</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>2051263.03792785</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>2042383.82250289</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>2011676.3093988</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>2240887.68697854</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>2581201.91080858</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2.963</t>
+          <t>2963357.73251987</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>3375554.56705043</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>3944366.02144599</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>4810828.23995541</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>4486795.96693829</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>17.578</t>
+          <t>17578474.7456917</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.826</t>
+          <t>17825902.783292</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17.622</t>
+          <t>17622048.5379238</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17.526</t>
+          <t>17525832.2310874</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18.139</t>
+          <t>18138832.5877258</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18.643</t>
+          <t>18642809.0924923</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18.571</t>
+          <t>18570731.973493</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>19189505.8865293</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>21.446</t>
+          <t>21446239.521659</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>23.768</t>
+          <t>23767828.4082607</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>25.436</t>
+          <t>25436229.899039</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>27.318</t>
+          <t>27318447.7177424</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>30.664</t>
+          <t>30664014.807903</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>33.891</t>
+          <t>33890653.6721761</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>32.314</t>
+          <t>32313568.4454114</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>compensation.emp.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
